--- a/4_outputs/final/Table32.xlsx
+++ b/4_outputs/final/Table32.xlsx
@@ -417,14 +417,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,6 +451,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Coverage gap adj. (ρ, p)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Research share excl. SDG 4 (ρ, p)</t>
         </is>
       </c>
@@ -467,17 +473,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.45 (0.071)</t>
+          <t>0.449 (0.071)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.01 (0.959)</t>
+          <t>-0.012 (0.959)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.61 (0.015)</t>
+          <t>0.544 (0.025)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.606 (0.015)</t>
         </is>
       </c>
     </row>
@@ -494,17 +505,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.06 (0.833)</t>
+          <t>-0.056 (0.833)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.22 (0.386)</t>
+          <t>-0.223 (0.386)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.05 (0.848)</t>
+          <t>-0.061 (0.807)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.053 (0.848)</t>
         </is>
       </c>
     </row>
@@ -521,17 +537,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.60 (0.014)</t>
+          <t>0.596 (0.014)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.04 (0.873)</t>
+          <t>0.042 (0.873)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.70 (0.003)</t>
+          <t>0.498 (0.044)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.703 (0.003)</t>
         </is>
       </c>
     </row>
@@ -548,17 +569,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.42 (0.115)</t>
+          <t>0.425 (0.115)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35 (0.195)</t>
+          <t>0.354 (0.195)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.61 (0.024)</t>
+          <t>0.357 (0.191)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.609 (0.024)</t>
         </is>
       </c>
     </row>
